--- a/powerapps/kolo-fortuny/sharepoint/Pytania_Kolo_Fortuny.xlsx
+++ b/powerapps/kolo-fortuny/sharepoint/Pytania_Kolo_Fortuny.xlsx
@@ -39,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7A1218"/>
+        <fgColor rgb="FFA32127"/>
       </patternFill>
     </fill>
   </fills>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -519,12 +519,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sernik z rodzynkami</t>
+          <t>Pizza z ananasem</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sernik bez rodzynek</t>
+          <t>Pizza bez ananasa</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pizza z ananasem</t>
+          <t>Ketchup na frytkach</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pizza bez ananasa</t>
+          <t>Ketchup obok</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ketchup na frytkach</t>
+          <t>Żurek</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ketchup obok</t>
+          <t>Barszcz</t>
         </is>
       </c>
     </row>
@@ -591,12 +591,12 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Żurek</t>
+          <t>Pierogi ruskie</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Barszcz</t>
+          <t>Pierogi z mięsem</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pierogi ruskie</t>
+          <t>Mielony</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pierogi z mięsem</t>
+          <t>Schabowy</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mielony</t>
+          <t>Kebab w bułce</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Schabowy</t>
+          <t>Kebab w tortilli</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kebab w bułce</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kebab w tortilli</t>
+          <t>Masło orzechowe</t>
         </is>
       </c>
     </row>
@@ -663,12 +663,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Hot dog jest kanapką</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Masło orzechowe</t>
+          <t>Hot dog nie jest kanapką</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hot dog jest kanapką</t>
+          <t>Pomidorowa z ryżem</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hot dog nie jest kanapką</t>
+          <t>Pomidorowa z makaronem</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pomidorowa z ryżem</t>
+          <t>Pizza rękami</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pomidorowa z makaronem</t>
+          <t>Pizza nożem i widelcem</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pizza rękami</t>
+          <t>Sernik z rodzynkami</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pizza nożem i widelcem</t>
+          <t>Sernik bez rodzynek</t>
         </is>
       </c>
     </row>
@@ -734,35 +734,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Śniadanie idealne to...</t>
+          <t>Gdyby trzeba było zrezygnować:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Świeże bułki</t>
+          <t>Nigdy więcej nie jeść</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chleb na zakwasie</t>
+          <t>Nigdy więcej nie spać</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Popkultura</t>
+          <t>Jedzenie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Star Wars</t>
+          <t>Śniadanie na kolację</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Star Trek</t>
+          <t>Kolacja na śniadanie</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Władca Pierścieni</t>
+          <t>Star Wars</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>Star Trek</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Władca Pierścieni</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The Office</t>
+          <t>Harry Potter</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>The Office</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iron Man</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Batman</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Iron Man</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HBO</t>
+          <t>Batman</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Książka</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Film</t>
+          <t>HBO</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kevin to film świąteczny</t>
+          <t>Książka</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kevin to nie film świąteczny</t>
+          <t>Film</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dzień świra</t>
+          <t>Napisy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kiler</t>
+          <t>Dubbing</t>
         </is>
       </c>
     </row>
@@ -916,19 +916,15 @@
           <t>Popkultura</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Oglądam zagraniczne filmy tak:</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Napisy</t>
+          <t>Kevin to film świąteczny</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dubbing</t>
+          <t>Kevin to nie film świąteczny</t>
         </is>
       </c>
     </row>
@@ -941,66 +937,66 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moda lat 80.</t>
+          <t>Dzień świra</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Moda lat 90.</t>
+          <t>Kiler</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>Popkultura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Biuro</t>
+          <t>Moda lat 80.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Home office</t>
+          <t>Moda lat 90.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>Popkultura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kamera włączona</t>
+          <t>Cały sezon jednego wieczoru</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Internet dziś słaby</t>
+          <t>Jeden odcinek tygodniowo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>Popkultura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Inbox Zero</t>
+          <t>Spoiler przed seansem</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12 847 nieprzeczytanych</t>
+          <t>Trzy godziny niepewności</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1009,12 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dokumentacja</t>
+          <t>Biuro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Spokojnie, pamiętam</t>
+          <t>Home office</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1027,12 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Power Apps</t>
+          <t>Kamera włączona</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Power Automate</t>
+          <t>Internet dziś słaby</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1045,12 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Inbox Zero</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PowerPoint</t>
+          <t>12 847 nieprzeczytanych</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1063,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Praca w ciszy</t>
+          <t>Dokumentacja</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Muzyka w tle</t>
+          <t>Spokojnie, pamiętam</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1081,12 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spotkanie o 8:00</t>
+          <t>Power Apps</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Spotkanie o 16:00</t>
+          <t>Power Automate</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1099,12 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>PowerPoint</t>
         </is>
       </c>
     </row>
@@ -1118,109 +1114,105 @@
           <t>Praca</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bez tego nie ruszam z miejsca:</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kawa z automatu</t>
+          <t>Praca w ciszy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Kawa z ekspresu</t>
+          <t>Muzyka w tle</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Styl życia</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Góry</t>
+          <t>Spotkanie o 8:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Morze</t>
+          <t>Spotkanie o 16:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Styl życia</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kot</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pies</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Styl życia</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rower</t>
+          <t>Cztery dni po dziesięć godzin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bieganie</t>
+          <t>Pięć dni po osiem</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Styl życia</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Nigdy więcej maili</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nigdy więcej spotkań</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Styl życia</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lato</t>
+          <t>Deadline dziś</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Zima</t>
+          <t>Deadline w piątek</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1225,12 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ranny ptaszek</t>
+          <t>Góry</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nocny marek</t>
+          <t>Morze</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1243,12 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Planowanie</t>
+          <t>Kot</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Spontaniczność</t>
+          <t>Pies</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1261,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Introwertyk</t>
+          <t>Rower</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ekstrawertyk</t>
+          <t>Bieganie</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1279,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Podcast</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Muzyka</t>
+          <t>Apple</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1297,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>City break</t>
+          <t>Lato</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>All inclusive</t>
+          <t>Zima</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1315,12 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Namiot</t>
+          <t>Ranny ptaszek</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Nocny marek</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1333,12 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Papier toaletowy od ściany</t>
+          <t>Planowanie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Papier toaletowy do ściany</t>
+          <t>Spontaniczność</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1351,12 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Śpiewanie w samochodzie</t>
+          <t>Introwertyk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Śpiewanie pod prysznicem</t>
+          <t>Ekstrawertyk</t>
         </is>
       </c>
     </row>
@@ -1374,147 +1366,195 @@
           <t>Styl życia</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Gdybym mógł wybrać supermoc:</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Latanie</t>
+          <t>Podcast</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Teleportacja</t>
+          <t>Muzyka</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Otwarte</t>
+          <t>Styl życia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jaka potrawa jest kompletnie przereklamowana?</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>City break</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>All inclusive</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Otwarte</t>
+          <t>Styl życia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jaki kultowy film Cię ominął?</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Namiot</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Otwarte</t>
+          <t>Styl życia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jaki zwrot z korpomowy najbardziej Cię denerwuje?</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Papier toaletowy od ściany</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Papier toaletowy do ściany</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Otwarte</t>
+          <t>Styl życia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jakie spotkanie mogło być mailem?</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Śpiewanie w samochodzie</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Śpiewanie pod prysznicem</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Otwarte</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>Styl życia</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gdybyś dostał supermoc:</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Co zawsze pakujesz na wyjazd, a potem tego nie używasz?</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Latanie</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Niewidzialność</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Otwarte</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>Styl życia</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gdybyś dostał supermoc:</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jaki skrót klawiszowy najbardziej ułatwia Ci życie?</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Podróże w czasie</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Czytanie w myślach</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Otwarte</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>Styl życia</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mieszkasz tam przez rok:</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jaka jest Twoja najbardziej niepopularna opinia?</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Domek w górach</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Chata na bezludnej wyspie</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Otwarte</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>Styl życia</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Do końca życia możesz:</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Co większość ludzi uważa za świetne, a Ty tego nie znosisz?</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Tylko szeptać</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Tylko krzyczeć</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Otwarte</t>
+          <t>Styl życia</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gdybyś jadł tylko jedną kuchnię do końca życia, jaką wybierasz?</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Zawsze za wcześnie</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Zawsze pięć minut za późno</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1525,10 +1565,164 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Jaka potrawa jest kompletnie przereklamowana?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Jaki kultowy film Cię ominął?</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Jaki zwrot z korpomowy najbardziej Cię denerwuje?</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Jakie spotkanie mogło być mailem?</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Co zawsze pakujesz na wyjazd, a potem tego nie używasz?</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jaki skrót klawiszowy najbardziej ułatwia Ci życie?</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jaka jest Twoja najbardziej niepopularna opinia?</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Co większość ludzi uważa za świetne, a Ty tego nie znosisz?</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Gdybyś jadł tylko jedną kuchnię do końca życia, jaką wybierasz?</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
           <t>Czego nauczyłeś się w tym roku, a szkoda, że nie wcześniej?</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Jaką umiejętność opanowałbyś natychmiast, gdyby się dało?</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Otwarte</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Co robisz, gdy nikt nie patrzy, a wcale się tego nie wstydzisz?</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
